--- a/Gerard i Òscar/PH_GerardMoreno_ÒscarLosada_M1.xlsx
+++ b/Gerard i Òscar/PH_GerardMoreno_ÒscarLosada_M1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uab-my.sharepoint.com/personal/1598367_uab_cat/Documents/5è CURS/LACE/Lab LACE - Gerard i Òscar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deumenec/Documents/Uni/LACE/Gerard i Òscar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="559" documentId="11_76D4419BBD0DC5B4564594EB90AF1A60D1CE558E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A0238C9-CCEF-4B5E-8499-1B8578BD0BB3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9E5AD3-C138-0D46-960E-742E1867278F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pràctica H" sheetId="1" r:id="rId1"/>
@@ -812,6 +812,42 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -839,47 +875,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -905,7 +905,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2941,7 +2941,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AW57"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="1" customWidth="1"/>
@@ -2949,15 +2949,15 @@
     <col min="5" max="5" width="19.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
     <col min="7" max="49" width="14.6640625" style="1" customWidth="1"/>
-    <col min="50" max="16384" width="11.44140625" style="1"/>
+    <col min="50" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -2970,13 +2970,13 @@
       <c r="F2" s="25">
         <v>45755</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="3" spans="1:11" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+    </row>
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -2989,70 +2989,70 @@
       <c r="F3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-    </row>
-    <row r="4" spans="1:11" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+    </row>
+    <row r="4" spans="1:11" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="C4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-    </row>
-    <row r="5" spans="1:11" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+    </row>
+    <row r="5" spans="1:11" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-    </row>
-    <row r="6" spans="1:11" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59" t="s">
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+    </row>
+    <row r="6" spans="1:11" ht="71" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="61"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-    </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="47"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H7" s="38" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="84.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="46" t="s">
+    <row r="9" spans="1:11" ht="84.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
       <c r="H9"/>
     </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -3077,17 +3077,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55" t="s">
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="56"/>
+      <c r="B16" s="43"/>
       <c r="C16" s="2">
         <v>0.1003</v>
       </c>
@@ -3098,45 +3098,45 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
+    <row r="17" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="56"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="26">
         <v>250</v>
       </c>
     </row>
-    <row r="18" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="H18"/>
     </row>
-    <row r="19" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="55" t="s">
+    <row r="19" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="56"/>
+      <c r="B19" s="43"/>
       <c r="C19" s="22">
         <v>0.248</v>
       </c>
     </row>
-    <row r="20" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="55" t="s">
+    <row r="20" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="56"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="26">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="22" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:49" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" ht="30" x14ac:dyDescent="0.15">
       <c r="A23" s="11" t="s">
         <v>27</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3">
         <f>$E$12/10</f>
         <v>99.8</v>
@@ -3185,7 +3185,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3">
         <f t="shared" ref="A25:A28" si="0">$E$12/10</f>
         <v>99.8</v>
@@ -3207,7 +3207,7 @@
         <v>3.8210000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>99.8</v>
@@ -3229,7 +3229,7 @@
         <v>3.8079999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>99.8</v>
@@ -3251,7 +3251,7 @@
         <v>3.8090000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>99.8</v>
@@ -3273,7 +3273,7 @@
         <v>3.7919999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -3281,7 +3281,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3289,8 +3289,8 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -3356,97 +3356,97 @@
       <c r="AV32" s="4"/>
       <c r="AW32" s="5"/>
     </row>
-    <row r="33" spans="1:49" ht="300" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="50"/>
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="52"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="52"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
-      <c r="R33" s="51"/>
-      <c r="S33" s="52"/>
-      <c r="T33" s="50"/>
-      <c r="U33" s="51"/>
-      <c r="V33" s="51"/>
-      <c r="W33" s="51"/>
-      <c r="X33" s="51"/>
-      <c r="Y33" s="52"/>
-      <c r="Z33" s="50"/>
-      <c r="AA33" s="51"/>
-      <c r="AB33" s="51"/>
-      <c r="AC33" s="51"/>
-      <c r="AD33" s="51"/>
-      <c r="AE33" s="52"/>
-      <c r="AF33" s="50"/>
-      <c r="AG33" s="51"/>
-      <c r="AH33" s="51"/>
-      <c r="AI33" s="51"/>
-      <c r="AJ33" s="51"/>
-      <c r="AK33" s="52"/>
-      <c r="AL33" s="50"/>
-      <c r="AM33" s="51"/>
-      <c r="AN33" s="51"/>
-      <c r="AO33" s="51"/>
-      <c r="AP33" s="51"/>
-      <c r="AQ33" s="52"/>
-      <c r="AR33" s="50"/>
-      <c r="AS33" s="51"/>
-      <c r="AT33" s="51"/>
-      <c r="AU33" s="51"/>
-      <c r="AV33" s="51"/>
-      <c r="AW33" s="52"/>
-    </row>
-    <row r="34" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:49" ht="300" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="48"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="50"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="48"/>
+      <c r="O33" s="49"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="49"/>
+      <c r="R33" s="49"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="48"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="49"/>
+      <c r="W33" s="49"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="48"/>
+      <c r="AA33" s="49"/>
+      <c r="AB33" s="49"/>
+      <c r="AC33" s="49"/>
+      <c r="AD33" s="49"/>
+      <c r="AE33" s="50"/>
+      <c r="AF33" s="48"/>
+      <c r="AG33" s="49"/>
+      <c r="AH33" s="49"/>
+      <c r="AI33" s="49"/>
+      <c r="AJ33" s="49"/>
+      <c r="AK33" s="50"/>
+      <c r="AL33" s="48"/>
+      <c r="AM33" s="49"/>
+      <c r="AN33" s="49"/>
+      <c r="AO33" s="49"/>
+      <c r="AP33" s="49"/>
+      <c r="AQ33" s="50"/>
+      <c r="AR33" s="48"/>
+      <c r="AS33" s="49"/>
+      <c r="AT33" s="49"/>
+      <c r="AU33" s="49"/>
+      <c r="AV33" s="49"/>
+      <c r="AW33" s="50"/>
+    </row>
+    <row r="34" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="47"/>
+      <c r="C34" s="59"/>
       <c r="D34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="53" t="s">
+      <c r="E34" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="F34" s="54"/>
-    </row>
-    <row r="35" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="61"/>
+    </row>
+    <row r="35" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="47"/>
+      <c r="C35" s="59"/>
       <c r="D35" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="48">
+      <c r="E35" s="40">
         <f>COUNT(D24:D30)</f>
         <v>5</v>
       </c>
-      <c r="F35" s="49"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H35" s="48">
+      <c r="H35" s="40">
         <v>0.999</v>
       </c>
-      <c r="I35" s="49"/>
-    </row>
-    <row r="36" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I35" s="41"/>
+    </row>
+    <row r="36" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -3454,7 +3454,7 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
     </row>
-    <row r="37" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
         <v>51</v>
       </c>
@@ -3462,32 +3462,32 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:49" ht="150.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="39" t="s">
+    <row r="38" spans="1:49" ht="150.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="40"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="41"/>
-      <c r="H38" s="39" t="s">
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
+      <c r="H38" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="40"/>
-      <c r="N38" s="40"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="40"/>
-      <c r="S38" s="41"/>
-    </row>
-    <row r="39" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="53"/>
+    </row>
+    <row r="39" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="33" t="s">
         <v>55</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="33" t="s">
         <v>61</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>0.35864295177815714</v>
       </c>
     </row>
-    <row r="42" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="34" t="s">
         <v>62</v>
       </c>
@@ -3562,13 +3562,13 @@
         <v>0.31986063849972696</v>
       </c>
     </row>
-    <row r="43" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="37" t="s">
         <v>64</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="37" t="s">
         <v>61</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>2.8448702313121625</v>
       </c>
     </row>
-    <row r="47" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="37" t="s">
         <v>62</v>
       </c>
@@ -3602,8 +3602,8 @@
         <v>0.41045939806417114</v>
       </c>
     </row>
-    <row r="48" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="6" t="s">
         <v>66</v>
       </c>
@@ -3614,23 +3614,23 @@
       <c r="F49" s="5"/>
       <c r="G49" s="13"/>
     </row>
-    <row r="50" spans="1:13" ht="199.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="42" t="s">
+    <row r="50" spans="1:13" ht="200" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="44"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
-      <c r="M50" s="45"/>
-    </row>
-    <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="55"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="56"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="57"/>
+      <c r="K50" s="57"/>
+      <c r="L50" s="57"/>
+      <c r="M50" s="57"/>
+    </row>
+    <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="7"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
@@ -3639,7 +3639,7 @@
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
     </row>
-    <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="7" t="s">
         <v>68</v>
       </c>
@@ -3650,17 +3650,17 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
     </row>
-    <row r="53" spans="1:13" ht="300" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="39" t="s">
+    <row r="53" spans="1:13" ht="300" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
-      <c r="F53" s="41"/>
-    </row>
-    <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="53"/>
+    </row>
+    <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -3669,7 +3669,7 @@
       <c r="F54" s="13"/>
       <c r="G54" s="13"/>
     </row>
-    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="13"/>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -3678,7 +3678,7 @@
       <c r="F55" s="13"/>
       <c r="G55" s="13"/>
     </row>
-    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="13"/>
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
@@ -3687,7 +3687,7 @@
       <c r="F56" s="13"/>
       <c r="G56" s="13"/>
     </row>
-    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="13"/>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
@@ -3698,18 +3698,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="H2:J4"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="H5:J6"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="AL33:AQ33"/>
-    <mergeCell ref="AR33:AW33"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="T33:Y33"/>
-    <mergeCell ref="Z33:AE33"/>
-    <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="H38:S38"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="H50:M50"/>
@@ -3724,6 +3712,18 @@
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="AL33:AQ33"/>
+    <mergeCell ref="AR33:AW33"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="T33:Y33"/>
+    <mergeCell ref="Z33:AE33"/>
+    <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="H2:J4"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="H5:J6"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{A346554D-ABD9-4C6D-B037-A5BBD4C4FCDC}"/>
@@ -3740,14 +3740,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" s="20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
       <c r="C4" s="62" t="s">
         <v>71</v>
@@ -3755,7 +3755,7 @@
       <c r="D4" s="62"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="18" t="s">
         <v>72</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="18" t="s">
         <v>74</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="18" t="s">
         <v>50</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="18" t="s">
         <v>77</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="18" t="s">
         <v>79</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="20" t="s">
         <v>82</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>-17944.046875000058</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="20" t="s">
         <v>83</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>449964</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="20" t="s">
         <v>84</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>203.98161919999993</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="20" t="s">
         <v>85</v>
       </c>
@@ -3879,7 +3879,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CBF7D5-4796-4DA5-BE23-F64CC8202AE4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
